--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
@@ -470,7 +470,7 @@
     <t xml:space="preserve">欢迎回来。快乐的时间就要这样结束了呀。再见，勇敢的客人。希望你可以用得到的宝物幸福地生活下去。</t>
   </si>
   <si>
-    <t xml:space="preserve">…哎？什么，这脏兮兮的纸片是怎么回事？</t>
+    <t xml:space="preserve">…诶？什么，这脏兮兮的纸片是怎么回事？</t>
   </si>
   <si>
     <t xml:space="preserve">和梅丽利丝做朋友券…嗯…这是我几百年前做的东西，但谁都没有用过它。我都忘得一干二净了。你…是特地为了这个放弃了其他的宝物吗？</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">…也是啊。你肯定也觉得那张纸片有没什么价值吧？…希望你被诅咒。</t>
   </si>
   <si>
-    <t xml:space="preserve">…哎？</t>
+    <t xml:space="preserve">…诶？</t>
   </si>
   <si>
     <t xml:space="preserve">你为了那张破纸片放弃了宝物？</t>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
@@ -503,7 +503,7 @@
     <t xml:space="preserve">我问你，这种时候，我该露出什么表情呢？我已经不记得活着的时候的事了…其实，就算是我还活着的时候也没有过…</t>
   </si>
   <si>
-    <t xml:space="preserve">谢谢你，我的第一个朋友。</t>
+    <t xml:space="preserve">谢谢你，我的第一位朋友。</t>
   </si>
 </sst>
 </file>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="melilith" sheetId="1" r:id="rId3"/>
+    <sheet name="melilith" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -211,7 +211,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family/>
+        <family val="0"/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">ここを訪れてくれるお客さんは少ないのよ。呪われた館なんて、ひどい名前で呼ぶ人もいるわ。ねえ、あなた…私と遊んでくれる？</t>
@@ -421,89 +421,6 @@
   </si>
   <si>
     <t xml:space="preserve">invoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">你是…迷路了？还是来玩的？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">哎呀，怎么了…#brother2？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎来到我的宅邸。虽说有些破旧凌乱，但请慢慢享受吧。我的名字是梅丽利丝。是不是像是城堡里公主一样的名字呢？
-到这里的访客并不多呢。毕竟这是个被称为诅咒洋馆的地方。你…愿意和我一起玩吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">好的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不要</t>
-  </si>
-  <si>
-    <t xml:space="preserve">这样啊…也是呢。谁也不会想在这种又阴暗又古旧的洋馆里玩呢…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真的吗？…好开心！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">其实…我唯一的乐趣就是和偶尔来访的客人玩游戏了。我们玩什么样的游戏好呢？捉迷藏？抓鬼？…啊，对了，你好像是冒险者，那我们去寻宝吧！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很久以前，我在这个洋馆的地下深处收集了很多宝物。其中有着能实现任何愿望的法杖。所以呢，有件事想拜托你…能帮我去寻找宝物吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">真的吗？…啊，你可真好！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你可以从找到的宝物中挑一个带走。但要注意！只能带走「一个」哦。不然的话，就会带来可怕的诅咒。
-那么，我们马上准备开始吧。嘿嘿，距离上次「寻宝」已经隔了几百年了呢？我真的很开心…一定要叫很多朋友来欢迎你才行！你…不害怕不死生物吧？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">那么，游戏马上就要开始了…准备好了的话，就去通往地下的楼梯吧。小心点，勇敢的冒险者。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">寻宝有进展吗？…我相信你一定能把美妙的悲鸣献给我们的。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欢迎回来。快乐的时间就要这样结束了呀。再见，勇敢的客人。希望你可以用得到的宝物幸福地生活下去。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…诶？什么，这脏兮兮的纸片是怎么回事？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">和梅丽利丝做朋友券…嗯…这是我几百年前做的东西，但谁都没有用过它。我都忘得一干二净了。你…是特地为了这个放弃了其他的宝物吗？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">没错</t>
-  </si>
-  <si>
-    <t xml:space="preserve">并不是</t>
-  </si>
-  <si>
-    <t xml:space="preserve">骗子。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…也是啊。你肯定也觉得那张纸片有没什么价值吧？…希望你被诅咒。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…诶？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你为了那张破纸片放弃了宝物？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">…寻宝游戏原本并没有这么危险。我以为一定会有人很快拿到它，然后微笑着带给我。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">但是，所有人都选了其他闪闪发光的宝物，然后离开了洋馆…所以我…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我问你，这种时候，我该露出什么表情呢？我已经不记得活着的时候的事了…其实，就算是我还活着的时候也没有过…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">谢谢你，我的第一位朋友。</t>
   </si>
 </sst>
 </file>
@@ -524,19 +441,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -549,7 +466,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -570,7 +487,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -596,7 +513,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -605,62 +522,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -674,13 +591,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -856,25 +773,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
-    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
-    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -909,23 +826,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="H2" s="1">
-        <f>MAX(H4:H1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H2" s="1" t="n">
+        <f aca="false">MAX(H4:H1048576)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" ht="12.8">
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -933,7 +850,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="14.9">
+    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -941,7 +858,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" ht="12.8">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
@@ -949,13 +866,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" ht="12.8">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" ht="13.8">
-      <c r="H14" s="1">
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
@@ -964,27 +881,24 @@
       <c r="J14" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K14" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" ht="12.8">
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" ht="12.8">
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" ht="12.8">
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
-      <c r="H20" s="1">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="1" t="n">
         <v>2</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -993,11 +907,8 @@
       <c r="J20" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K20" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" ht="12.8">
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D21" s="1" t="s">
         <v>25</v>
       </c>
@@ -1006,23 +917,23 @@
       </c>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" ht="12.8">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" ht="12.8">
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
@@ -1030,7 +941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" ht="12.8">
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
@@ -1038,7 +949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" ht="12.8">
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
@@ -1046,8 +957,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" ht="13.8">
-      <c r="H28" s="1">
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="1" t="n">
         <v>3</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -1056,12 +967,9 @@
       <c r="J28" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K28" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" ht="94.75">
-      <c r="H29" s="1">
+    </row>
+    <row r="29" customFormat="false" ht="94.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H29" s="1" t="n">
         <v>4</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -1070,18 +978,15 @@
       <c r="J29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K29" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30" ht="12.8">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="1" t="n">
         <v>5</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -1090,18 +995,15 @@
       <c r="J30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K30" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="31" ht="12.8">
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="1" t="n">
         <v>6</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -1110,20 +1012,17 @@
       <c r="J31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K31" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="32" ht="12.8">
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D32" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" ht="23.85">
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="1" t="n">
         <v>7</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -1132,22 +1031,19 @@
       <c r="J34" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="K34" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" ht="12.8">
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" ht="12.8">
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" ht="13.8">
-      <c r="H39" s="1">
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H39" s="1" t="n">
         <v>8</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -1156,12 +1052,9 @@
       <c r="J39" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K39" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" ht="57.45">
-      <c r="H40" s="1">
+    </row>
+    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H40" s="1" t="n">
         <v>9</v>
       </c>
       <c r="I40" s="5" t="s">
@@ -1170,12 +1063,9 @@
       <c r="J40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="K40" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="41" ht="46.25">
-      <c r="H41" s="1">
+    </row>
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H41" s="1" t="n">
         <v>10</v>
       </c>
       <c r="I41" s="5" t="s">
@@ -1184,18 +1074,15 @@
       <c r="J41" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K41" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="1" t="n">
         <v>11</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -1204,18 +1091,15 @@
       <c r="J42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="43" ht="12.8">
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -1224,17 +1108,14 @@
       <c r="J43" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K43" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="47" ht="12.8">
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" ht="13.8">
-      <c r="H48" s="1">
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H48" s="1" t="n">
         <v>13</v>
       </c>
       <c r="I48" s="5" t="s">
@@ -1243,12 +1124,9 @@
       <c r="J48" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="K48" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" ht="113.4">
-      <c r="H49" s="1">
+    </row>
+    <row r="49" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H49" s="1" t="n">
         <v>14</v>
       </c>
       <c r="I49" s="5" t="s">
@@ -1257,11 +1135,8 @@
       <c r="J49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="K49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" ht="13.8">
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D50" s="1" t="s">
         <v>55</v>
       </c>
@@ -1271,7 +1146,7 @@
       <c r="I50" s="5"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" ht="13.8">
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1279,18 +1154,18 @@
       <c r="I51" s="5"/>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" ht="13.8">
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="7" t="n">
         <v>27</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" ht="35.05">
-      <c r="H53" s="1">
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H53" s="1" t="n">
         <v>15</v>
       </c>
       <c r="I53" s="5" t="s">
@@ -1299,20 +1174,17 @@
       <c r="J53" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="K53" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" ht="12.8">
+    </row>
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" ht="35.05">
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H56" s="1">
+      <c r="H56" s="1" t="n">
         <v>16</v>
       </c>
       <c r="I56" s="5" t="s">
@@ -1321,25 +1193,22 @@
       <c r="J56" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="K56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="57" ht="13.8">
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I57" s="5"/>
     </row>
-    <row r="58" ht="12.8">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="65" ht="12.8">
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="66" ht="37.3">
-      <c r="H66" s="1">
+    <row r="66" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H66" s="1" t="n">
         <v>17</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -1348,11 +1217,8 @@
       <c r="J66" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="K66" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="67" ht="12.8">
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
@@ -1361,7 +1227,7 @@
       </c>
       <c r="E67" s="7"/>
     </row>
-    <row r="68" ht="12.8">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D68" s="1" t="s">
         <v>66</v>
       </c>
@@ -1369,13 +1235,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" ht="12.8">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E69" s="7"/>
     </row>
-    <row r="70" ht="12.8">
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
@@ -1383,19 +1249,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" ht="12.8">
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="73" ht="13.8">
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>67</v>
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" ht="13.8">
-      <c r="H74" s="1">
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H74" s="1" t="n">
         <v>18</v>
       </c>
       <c r="I74" s="5" t="s">
@@ -1404,12 +1270,9 @@
       <c r="J74" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K74" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="75" ht="46.25">
-      <c r="H75" s="1">
+    </row>
+    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H75" s="1" t="n">
         <v>19</v>
       </c>
       <c r="I75" s="5" t="s">
@@ -1418,18 +1281,15 @@
       <c r="J75" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="K75" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="76" ht="12.8">
+    </row>
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H76" s="1">
+      <c r="H76" s="1" t="n">
         <v>20</v>
       </c>
       <c r="I76" s="3" t="s">
@@ -1438,18 +1298,15 @@
       <c r="J76" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="K76" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="77" ht="12.8">
+    </row>
+    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H77" s="1">
+      <c r="H77" s="1" t="n">
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
@@ -1458,17 +1315,14 @@
       <c r="J77" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K77" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="79" ht="12.8">
+    </row>
+    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="80" ht="12.8">
-      <c r="H80" s="1">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H80" s="1" t="n">
         <v>31</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -1477,18 +1331,15 @@
       <c r="J80" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="K80" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="81" ht="13.8">
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>74</v>
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" ht="37.3">
-      <c r="H82" s="1">
+    <row r="82" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H82" s="1" t="n">
         <v>22</v>
       </c>
       <c r="I82" s="6" t="s">
@@ -1497,29 +1348,26 @@
       <c r="J82" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K82" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="83" ht="13.8">
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I83" s="6"/>
     </row>
-    <row r="84" ht="13.8">
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I84" s="6"/>
     </row>
-    <row r="85" ht="13.8">
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="I85" s="6"/>
     </row>
-    <row r="86" ht="13.8">
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" ht="13.8">
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="1" t="s">
         <v>75</v>
       </c>
@@ -1528,16 +1376,16 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" ht="13.8">
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D88" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E88" s="1">
+      <c r="E88" s="1" t="n">
         <v>12</v>
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" ht="12.8">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D89" s="1" t="s">
         <v>81</v>
       </c>
@@ -1545,8 +1393,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" ht="12.8">
-      <c r="H90" s="1">
+    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H90" s="1" t="n">
         <v>24</v>
       </c>
       <c r="I90" s="3" t="s">
@@ -1555,12 +1403,9 @@
       <c r="J90" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K90" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="91" ht="22.35">
-      <c r="H91" s="1">
+    </row>
+    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H91" s="1" t="n">
         <v>27</v>
       </c>
       <c r="I91" s="3" t="s">
@@ -1569,12 +1414,9 @@
       <c r="J91" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K91" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="92" ht="32.8">
-      <c r="H92" s="1">
+    </row>
+    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H92" s="1" t="n">
         <v>28</v>
       </c>
       <c r="I92" s="3" t="s">
@@ -1583,12 +1425,9 @@
       <c r="J92" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="K92" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="93" ht="22.35">
-      <c r="H93" s="1">
+    </row>
+    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H93" s="1" t="n">
         <v>29</v>
       </c>
       <c r="I93" s="3" t="s">
@@ -1597,12 +1436,9 @@
       <c r="J93" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K93" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="94" ht="12.8">
-      <c r="H94" s="1">
+    </row>
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H94" s="1" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="3" t="s">
@@ -1611,12 +1447,9 @@
       <c r="J94" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K94" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" ht="32.8">
-      <c r="H95" s="1">
+    </row>
+    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H95" s="1" t="n">
         <v>25</v>
       </c>
       <c r="I95" s="3" t="s">
@@ -1625,12 +1458,9 @@
       <c r="J95" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K95" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="96" ht="12.8">
-      <c r="H96" s="1">
+    </row>
+    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H96" s="1" t="n">
         <v>26</v>
       </c>
       <c r="I96" s="3" t="s">
@@ -1639,12 +1469,9 @@
       <c r="J96" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K96" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="97" ht="13.8">
-      <c r="H97" s="1">
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H97" s="1" t="n">
         <v>23</v>
       </c>
       <c r="I97" s="6" t="s">
@@ -1653,11 +1480,8 @@
       <c r="J97" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K97" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="98" ht="12.8">
+    </row>
+    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D98" s="1" t="s">
         <v>97</v>
       </c>
@@ -1665,7 +1489,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" ht="12.8">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D99" s="1" t="s">
         <v>99</v>
       </c>
@@ -1673,19 +1497,19 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" ht="12.8">
+    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="1" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23:H1048576 H4:H20 I21:I22">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/melilith.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="melilith" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="melilith" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="127">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -211,7 +211,7 @@
         <sz val="11"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
-        <family val="0"/>
+        <family/>
         <charset val="128"/>
       </rPr>
       <t xml:space="preserve">ここを訪れてくれるお客さんは少ないのよ。呪われた館なんて、ひどい名前で呼ぶ人もいるわ。ねえ、あなた…私と遊んでくれる？</t>
@@ -421,6 +421,89 @@
   </si>
   <si>
     <t xml:space="preserve">invoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">你是…迷路了？还是来玩的？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">哎呀，怎么了…#brother2？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎来到我的宅邸。虽说有些破旧凌乱，但请慢慢享受吧。我的名字是梅丽利丝。是不是像是城堡里公主一样的名字呢？
+到这里的访客并不多呢。毕竟这是个被称为诅咒洋馆的地方。你…愿意和我一起玩吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">好的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不要</t>
+  </si>
+  <si>
+    <t xml:space="preserve">这样啊…也是呢。谁也不会想在这种又阴暗又古旧的洋馆里玩呢…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真的吗？…好开心！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">其实…我唯一的乐趣就是和偶尔来访的客人玩游戏了。我们玩什么样的游戏好呢？捉迷藏？抓鬼？…啊，对了，你好像是冒险者，那我们去寻宝吧！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很久以前，我在这个洋馆的地下深处收集了很多宝物。其中有着能实现任何愿望的法杖。所以呢，有件事想拜托你…能帮我去寻找宝物吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">真的吗？…啊，你可真好！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你可以从找到的宝物中挑一个带走。但要注意！只能带走「一个」哦。不然的话，就会带来可怕的诅咒。
+那么，我们马上准备开始吧。嘿嘿，距离上次「寻宝」已经隔了几百年了呢？我真的很开心…一定要叫很多朋友来欢迎你才行！你…不害怕不死生物吧？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">那么，游戏马上就要开始了…准备好了的话，就去通往地下的楼梯吧。小心点，勇敢的冒险者。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">寻宝有进展吗？…我相信你一定能把美妙的悲鸣献给我们的。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欢迎回来。快乐的时间就要这样结束了呀。再见，勇敢的客人。希望你可以用得到的宝物幸福地生活下去。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…诶？什么，这脏兮兮的纸片是怎么回事？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">和梅丽利丝做朋友券…嗯…这是我几百年前做的东西，但谁都没有用过它。我都忘得一干二净了。你…是特地为了这个放弃了其他的宝物吗？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">没错</t>
+  </si>
+  <si>
+    <t xml:space="preserve">并不是</t>
+  </si>
+  <si>
+    <t xml:space="preserve">骗子。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…也是啊。你肯定也觉得那张纸片有没什么价值吧？…希望你被诅咒。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…诶？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你为了那张破纸片放弃了宝物？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…寻宝游戏原本并没有这么危险。我以为一定会有人很快拿到它，然后微笑着带给我。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">但是，所有人都选了其他闪闪发光的宝物，然后离开了洋馆…所以我…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我问你，这种时候，我该露出什么表情呢？我已经不记得活着的时候的事了…其实，就算是我还活着的时候也没有过…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">谢谢你，我的第一位朋友。</t>
   </si>
 </sst>
 </file>
@@ -441,19 +524,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -466,7 +549,7 @@
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -487,7 +570,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -513,7 +596,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -522,62 +605,62 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -591,13 +674,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -773,25 +856,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K100"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="2" width="53.28"/>
+    <col min="1" max="1" width="14.41" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.99" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.12" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85" style="1" customWidth="1"/>
+    <col min="7" max="8" width="7.09" style="1" customWidth="1"/>
+    <col min="9" max="9" width="42.14" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.28" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -826,23 +909,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H2" s="1" t="n">
-        <f aca="false">MAX(H4:H1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="H2" s="1">
+        <f>MAX(H4:H1048576)</f>
         <v>31</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" ht="12.8">
       <c r="B9" s="1" t="s">
         <v>13</v>
       </c>
@@ -850,7 +933,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="14.9">
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
@@ -858,7 +941,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" ht="12.8">
       <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
@@ -866,13 +949,13 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" ht="12.8">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H14" s="1" t="n">
+    <row r="14" ht="13.8">
+      <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="5" t="s">
@@ -881,24 +964,27 @@
       <c r="J14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" ht="12.8">
       <c r="D15" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" ht="12.8">
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" ht="12.8">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H20" s="1" t="n">
+    <row r="20" ht="12.8">
+      <c r="H20" s="1">
         <v>2</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -907,8 +993,11 @@
       <c r="J20" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K20" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="21" ht="12.8">
       <c r="D21" s="1" t="s">
         <v>25</v>
       </c>
@@ -917,23 +1006,23 @@
       </c>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" ht="12.8">
       <c r="D22" s="1" t="s">
         <v>21</v>
       </c>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" ht="12.8">
       <c r="D23" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="A24" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="B25" s="1" t="s">
         <v>27</v>
       </c>
@@ -941,7 +1030,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" ht="12.8">
       <c r="B26" s="1" t="s">
         <v>29</v>
       </c>
@@ -949,7 +1038,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" ht="12.8">
       <c r="B27" s="1" t="s">
         <v>29</v>
       </c>
@@ -957,8 +1046,8 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H28" s="1" t="n">
+    <row r="28" ht="13.8">
+      <c r="H28" s="1">
         <v>3</v>
       </c>
       <c r="I28" s="5" t="s">
@@ -967,9 +1056,12 @@
       <c r="J28" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="94.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H29" s="1" t="n">
+      <c r="K28" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" ht="94.75">
+      <c r="H29" s="1">
         <v>4</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -978,15 +1070,18 @@
       <c r="J29" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
       <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H30" s="1" t="n">
+      <c r="H30" s="1">
         <v>5</v>
       </c>
       <c r="I30" s="3" t="s">
@@ -995,15 +1090,18 @@
       <c r="J30" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" ht="12.8">
       <c r="B31" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="1" t="n">
+      <c r="H31" s="1">
         <v>6</v>
       </c>
       <c r="I31" s="3" t="s">
@@ -1012,17 +1110,20 @@
       <c r="J31" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="32" ht="12.8">
       <c r="D32" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="23.85">
       <c r="A34" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="H34" s="1" t="n">
+      <c r="H34" s="1">
         <v>7</v>
       </c>
       <c r="I34" s="5" t="s">
@@ -1031,19 +1132,22 @@
       <c r="J34" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K34" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" ht="12.8">
       <c r="B35" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" ht="12.8">
       <c r="A38" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H39" s="1" t="n">
+    <row r="39" ht="13.8">
+      <c r="H39" s="1">
         <v>8</v>
       </c>
       <c r="I39" s="5" t="s">
@@ -1052,9 +1156,12 @@
       <c r="J39" s="3" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="40" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H40" s="1" t="n">
+      <c r="K39" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" ht="57.45">
+      <c r="H40" s="1">
         <v>9</v>
       </c>
       <c r="I40" s="5" t="s">
@@ -1063,9 +1170,12 @@
       <c r="J40" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H41" s="1" t="n">
+      <c r="K40" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="41" ht="46.25">
+      <c r="H41" s="1">
         <v>10</v>
       </c>
       <c r="I41" s="5" t="s">
@@ -1074,15 +1184,18 @@
       <c r="J41" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="B42" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H42" s="1" t="n">
+      <c r="H42" s="1">
         <v>11</v>
       </c>
       <c r="I42" s="3" t="s">
@@ -1091,15 +1204,18 @@
       <c r="J42" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K42" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="43" ht="12.8">
       <c r="B43" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H43" s="1" t="n">
+      <c r="H43" s="1">
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
@@ -1108,14 +1224,17 @@
       <c r="J43" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="47" ht="12.8">
       <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H48" s="1" t="n">
+    <row r="48" ht="13.8">
+      <c r="H48" s="1">
         <v>13</v>
       </c>
       <c r="I48" s="5" t="s">
@@ -1124,9 +1243,12 @@
       <c r="J48" s="3" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H49" s="1" t="n">
+      <c r="K48" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" ht="113.4">
+      <c r="H49" s="1">
         <v>14</v>
       </c>
       <c r="I49" s="5" t="s">
@@ -1135,8 +1257,11 @@
       <c r="J49" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" ht="13.8">
       <c r="D50" s="1" t="s">
         <v>55</v>
       </c>
@@ -1146,7 +1271,7 @@
       <c r="I50" s="5"/>
       <c r="J50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" ht="13.8">
       <c r="D51" s="1" t="s">
         <v>57</v>
       </c>
@@ -1154,18 +1279,18 @@
       <c r="I51" s="5"/>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" ht="13.8">
       <c r="D52" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E52" s="7" t="n">
+      <c r="E52" s="7">
         <v>27</v>
       </c>
       <c r="I52" s="5"/>
       <c r="J52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H53" s="1" t="n">
+    <row r="53" ht="35.05">
+      <c r="H53" s="1">
         <v>15</v>
       </c>
       <c r="I53" s="5" t="s">
@@ -1174,17 +1299,20 @@
       <c r="J53" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="54" ht="12.8">
       <c r="B54" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" ht="35.05">
       <c r="A56" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H56" s="1" t="n">
+      <c r="H56" s="1">
         <v>16</v>
       </c>
       <c r="I56" s="5" t="s">
@@ -1193,22 +1321,25 @@
       <c r="J56" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K56" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" ht="13.8">
       <c r="I57" s="5"/>
     </row>
-    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" ht="12.8">
       <c r="B58" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" ht="12.8">
       <c r="A65" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H66" s="1" t="n">
+    <row r="66" ht="37.3">
+      <c r="H66" s="1">
         <v>17</v>
       </c>
       <c r="I66" s="6" t="s">
@@ -1217,8 +1348,11 @@
       <c r="J66" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" ht="12.8">
       <c r="B67" s="1" t="s">
         <v>65</v>
       </c>
@@ -1227,7 +1361,7 @@
       </c>
       <c r="E67" s="7"/>
     </row>
-    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" ht="12.8">
       <c r="D68" s="1" t="s">
         <v>66</v>
       </c>
@@ -1235,13 +1369,13 @@
         <v>56</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" ht="12.8">
       <c r="A69" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E69" s="7"/>
     </row>
-    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" ht="12.8">
       <c r="B70" s="1" t="s">
         <v>67</v>
       </c>
@@ -1249,19 +1383,19 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" ht="12.8">
       <c r="B71" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" ht="13.8">
       <c r="A73" s="1" t="s">
         <v>67</v>
       </c>
       <c r="I73" s="6"/>
     </row>
-    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H74" s="1" t="n">
+    <row r="74" ht="13.8">
+      <c r="H74" s="1">
         <v>18</v>
       </c>
       <c r="I74" s="5" t="s">
@@ -1270,9 +1404,12 @@
       <c r="J74" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H75" s="1" t="n">
+      <c r="K74" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="75" ht="46.25">
+      <c r="H75" s="1">
         <v>19</v>
       </c>
       <c r="I75" s="5" t="s">
@@ -1281,15 +1418,18 @@
       <c r="J75" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K75" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="76" ht="12.8">
       <c r="B76" s="1" t="s">
         <v>73</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H76" s="1" t="n">
+      <c r="H76" s="1">
         <v>20</v>
       </c>
       <c r="I76" s="3" t="s">
@@ -1298,15 +1438,18 @@
       <c r="J76" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K76" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="77" ht="12.8">
       <c r="B77" s="1" t="s">
         <v>74</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="H77" s="1" t="n">
+      <c r="H77" s="1">
         <v>21</v>
       </c>
       <c r="I77" s="3" t="s">
@@ -1315,14 +1458,17 @@
       <c r="J77" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K77" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" ht="12.8">
       <c r="A79" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H80" s="1" t="n">
+    <row r="80" ht="12.8">
+      <c r="H80" s="1">
         <v>31</v>
       </c>
       <c r="I80" s="3" t="s">
@@ -1331,15 +1477,18 @@
       <c r="J80" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K80" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="81" ht="13.8">
       <c r="A81" s="1" t="s">
         <v>74</v>
       </c>
       <c r="I81" s="6"/>
     </row>
-    <row r="82" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H82" s="1" t="n">
+    <row r="82" ht="37.3">
+      <c r="H82" s="1">
         <v>22</v>
       </c>
       <c r="I82" s="6" t="s">
@@ -1348,26 +1497,29 @@
       <c r="J82" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K82" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" ht="13.8">
       <c r="B83" s="1" t="s">
         <v>43</v>
       </c>
       <c r="I83" s="6"/>
     </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" ht="13.8">
       <c r="I84" s="6"/>
     </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" ht="13.8">
       <c r="I85" s="6"/>
     </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" ht="13.8">
       <c r="A86" s="1" t="s">
         <v>73</v>
       </c>
       <c r="I86" s="6"/>
     </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" ht="13.8">
       <c r="B87" s="1" t="s">
         <v>75</v>
       </c>
@@ -1376,16 +1528,16 @@
       </c>
       <c r="I87" s="6"/>
     </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" ht="13.8">
       <c r="D88" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E88" s="1">
         <v>12</v>
       </c>
       <c r="I88" s="6"/>
     </row>
-    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" ht="12.8">
       <c r="D89" s="1" t="s">
         <v>81</v>
       </c>
@@ -1393,8 +1545,8 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H90" s="1" t="n">
+    <row r="90" ht="12.8">
+      <c r="H90" s="1">
         <v>24</v>
       </c>
       <c r="I90" s="3" t="s">
@@ -1403,9 +1555,12 @@
       <c r="J90" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="91" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H91" s="1" t="n">
+      <c r="K90" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="91" ht="22.35">
+      <c r="H91" s="1">
         <v>27</v>
       </c>
       <c r="I91" s="3" t="s">
@@ -1414,9 +1569,12 @@
       <c r="J91" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="92" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H92" s="1" t="n">
+      <c r="K91" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="92" ht="32.8">
+      <c r="H92" s="1">
         <v>28</v>
       </c>
       <c r="I92" s="3" t="s">
@@ -1425,9 +1583,12 @@
       <c r="J92" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="93" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H93" s="1" t="n">
+      <c r="K92" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="93" ht="22.35">
+      <c r="H93" s="1">
         <v>29</v>
       </c>
       <c r="I93" s="3" t="s">
@@ -1436,9 +1597,12 @@
       <c r="J93" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H94" s="1" t="n">
+      <c r="K93" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="94" ht="12.8">
+      <c r="H94" s="1">
         <v>30</v>
       </c>
       <c r="I94" s="3" t="s">
@@ -1447,9 +1611,12 @@
       <c r="J94" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="95" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H95" s="1" t="n">
+      <c r="K94" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="95" ht="32.8">
+      <c r="H95" s="1">
         <v>25</v>
       </c>
       <c r="I95" s="3" t="s">
@@ -1458,9 +1625,12 @@
       <c r="J95" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H96" s="1" t="n">
+      <c r="K95" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="96" ht="12.8">
+      <c r="H96" s="1">
         <v>26</v>
       </c>
       <c r="I96" s="3" t="s">
@@ -1469,9 +1639,12 @@
       <c r="J96" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H97" s="1" t="n">
+      <c r="K96" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="97" ht="13.8">
+      <c r="H97" s="1">
         <v>23</v>
       </c>
       <c r="I97" s="6" t="s">
@@ -1480,8 +1653,11 @@
       <c r="J97" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K97" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="98" ht="12.8">
       <c r="D98" s="1" t="s">
         <v>97</v>
       </c>
@@ -1489,7 +1665,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" ht="12.8">
       <c r="D99" s="1" t="s">
         <v>99</v>
       </c>
@@ -1497,19 +1673,19 @@
         <v>98</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" ht="12.8">
       <c r="B100" s="1" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="H23:H1048576 H4:H20 I21:I22">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
